--- a/Vehicle_Planing_Trial.xlsx
+++ b/Vehicle_Planing_Trial.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sma-screens/Documents/Claude/Projects/Vehicle Planning Dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://screensgroup-my.sharepoint.com/personal/driveone_screensauto_com/Documents/CONS/6_Further Projects/Global-IIC-Map/Live Version/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8522F446-FAB0-6041-9E06-A5BDB3847A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{8522F446-FAB0-6041-9E06-A5BDB3847A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3DE16FA-F028-4745-9FE9-0850BC63DF02}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17080" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="322">
   <si>
     <t>KALENDER</t>
   </si>
@@ -216,9 +216,6 @@
     <t>Smart</t>
   </si>
   <si>
-    <t>#5</t>
-  </si>
-  <si>
     <t>Cadillac</t>
   </si>
   <si>
@@ -1006,6 +1003,12 @@
   </si>
   <si>
     <t>CX-5</t>
+  </si>
+  <si>
+    <t>KIA</t>
+  </si>
+  <si>
+    <t>PV5 Passenger</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1233,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="58">
+  <borders count="61">
     <border>
       <left/>
       <right/>
@@ -1947,12 +1950,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2329,11 +2373,20 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2636,18 +2689,18 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
-          <color rgb="FF000000"/>
+          <color theme="1"/>
         </left>
         <right style="medium">
-          <color rgb="FF000000"/>
+          <color theme="1"/>
         </right>
         <top style="medium">
-          <color rgb="FF000000"/>
+          <color theme="1"/>
         </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
+        <bottom style="medium">
+          <color theme="1"/>
         </bottom>
       </border>
     </dxf>
@@ -2716,25 +2769,21 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3C4E527C-4544-48AF-B672-0BE2D4C7DA67}" name="Table6432" displayName="Table6432" ref="A3:H202" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" tableBorderDxfId="8">
-  <autoFilter ref="A3:H202" xr:uid="{C371DFBA-4EE2-41E3-B277-F40937280E4B}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:H200">
-    <sortCondition descending="1" ref="A3:A200"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FF8F4864-84CF-4A49-8715-95EEF635F2FC}" name="Table64323" displayName="Table64323" ref="A3:H201" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" tableBorderDxfId="8">
+  <autoFilter ref="A3:H201" xr:uid="{FF8F4864-84CF-4A49-8715-95EEF635F2FC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:H201">
+    <sortCondition descending="1" ref="A3:A201"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{E05DA704-F0AF-4EB2-9006-68D297BDD92F}" name="No " dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{2D8226A3-604E-4511-B158-CCE1C63B4B26}" name="Car brands" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{0E2164B2-0669-4BE2-88E0-F4808A8473CC}" name="Models" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{F2C16AFF-893D-478C-92C9-A666F442455C}" name="EU" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{6DA762D1-9143-431E-8A4B-3197BC2B1EF9}" name="US" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{22D0B006-E64A-456F-9A75-40F65EEE4F0A}" name="CN" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{9248A026-6EA6-4D3E-9EC4-A56EB4008E22}" name="Status" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{099FE200-98B0-4C5A-86F6-C80CDECEDE70}" name="Model Year" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{1066786C-47AD-4E4A-9070-1684DE927E14}" name="No " dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{B622E2F9-B622-774B-9968-D1FDF3A8CA2A}" name="Car brands" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{83D90E76-9A3D-064A-ABA9-1718410BF740}" name="Models" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{03F7D22A-54C2-4649-B96C-0E7F5B9A30D5}" name="EU" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{3DCA5C68-CADB-1E4A-9829-0900D1F923A2}" name="US" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{6EEC8C05-7F69-C743-8624-7E27B2CB9509}" name="CN" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{E9BA1C6F-0DBC-5C4F-A3BF-19131DF9D00C}" name="Status" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{4BD25993-5ECD-F140-BA16-C697565C5351}" name="Model Year" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3260,7 +3309,7 @@
       <c r="AJ4" s="20"/>
     </row>
     <row r="5" spans="1:48" ht="41.75" customHeight="1">
-      <c r="B5" s="126"/>
+      <c r="B5" s="127"/>
       <c r="C5" s="14" t="s">
         <v>4</v>
       </c>
@@ -3469,7 +3518,7 @@
       <c r="AJ8" s="20"/>
     </row>
     <row r="9" spans="1:48" ht="41.75" customHeight="1">
-      <c r="B9" s="127"/>
+      <c r="B9" s="126"/>
       <c r="C9" s="14" t="s">
         <v>4</v>
       </c>
@@ -3684,7 +3733,7 @@
       <c r="AJ12" s="20"/>
     </row>
     <row r="13" spans="1:48" ht="41.75" customHeight="1">
-      <c r="B13" s="127"/>
+      <c r="B13" s="126"/>
       <c r="C13" s="14" t="s">
         <v>4</v>
       </c>
@@ -3897,7 +3946,7 @@
       <c r="AJ16" s="20"/>
     </row>
     <row r="17" spans="2:36" ht="41.75" customHeight="1">
-      <c r="B17" s="127"/>
+      <c r="B17" s="126"/>
       <c r="C17" s="14" t="s">
         <v>4</v>
       </c>
@@ -4112,7 +4161,7 @@
       <c r="AJ20" s="20"/>
     </row>
     <row r="21" spans="2:36" ht="41.75" customHeight="1">
-      <c r="B21" s="127"/>
+      <c r="B21" s="126"/>
       <c r="C21" s="14" t="s">
         <v>4</v>
       </c>
@@ -4325,7 +4374,7 @@
       <c r="AJ24" s="20"/>
     </row>
     <row r="25" spans="2:36" ht="41.75" customHeight="1">
-      <c r="B25" s="127"/>
+      <c r="B25" s="126"/>
       <c r="C25" s="14" t="s">
         <v>4</v>
       </c>
@@ -4540,7 +4589,7 @@
       <c r="AJ28" s="20"/>
     </row>
     <row r="29" spans="2:36" ht="41.75" customHeight="1">
-      <c r="B29" s="127"/>
+      <c r="B29" s="126"/>
       <c r="C29" s="14" t="s">
         <v>4</v>
       </c>
@@ -4755,7 +4804,7 @@
       <c r="AJ32" s="20"/>
     </row>
     <row r="33" spans="2:36" ht="41.75" customHeight="1">
-      <c r="B33" s="127"/>
+      <c r="B33" s="126"/>
       <c r="C33" s="14" t="s">
         <v>4</v>
       </c>
@@ -4969,7 +5018,7 @@
       <c r="AJ36" s="40"/>
     </row>
     <row r="37" spans="2:36" ht="41.75" customHeight="1">
-      <c r="B37" s="127"/>
+      <c r="B37" s="126"/>
       <c r="C37" s="14" t="s">
         <v>4</v>
       </c>
@@ -5184,7 +5233,7 @@
       <c r="AJ40" s="20"/>
     </row>
     <row r="41" spans="2:36" ht="41.75" customHeight="1">
-      <c r="B41" s="127"/>
+      <c r="B41" s="126"/>
       <c r="C41" s="14" t="s">
         <v>4</v>
       </c>
@@ -5397,7 +5446,7 @@
       <c r="AJ44" s="20"/>
     </row>
     <row r="45" spans="2:36" ht="41.75" customHeight="1">
-      <c r="B45" s="127"/>
+      <c r="B45" s="126"/>
       <c r="C45" s="14" t="s">
         <v>4</v>
       </c>
@@ -5767,6 +5816,11 @@
     <row r="69" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B19:B21"/>
     <mergeCell ref="B23:B25"/>
     <mergeCell ref="B43:B45"/>
     <mergeCell ref="B47:B49"/>
@@ -5774,11 +5828,6 @@
     <mergeCell ref="B39:B41"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B19:B21"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <dataValidations xWindow="94" yWindow="951" count="5">
@@ -5928,24 +5977,24 @@
       <c r="Z3" s="76"/>
     </row>
     <row r="4" spans="1:26">
-      <c r="A4" s="106">
-        <v>199</v>
-      </c>
-      <c r="B4" s="108" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="108" t="s">
+      <c r="A4" s="128">
+        <v>200</v>
+      </c>
+      <c r="B4" s="129" t="s">
         <v>320</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="108">
+      <c r="C4" s="129" t="s">
+        <v>321</v>
+      </c>
+      <c r="D4" s="129" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="129"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="130">
         <v>2026</v>
       </c>
       <c r="I4" s="48"/>
@@ -5968,24 +6017,24 @@
       <c r="Z4" s="90"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="106">
-        <v>198</v>
-      </c>
-      <c r="B5" s="108" t="s">
-        <v>318</v>
-      </c>
-      <c r="C5" s="108" t="s">
+      <c r="A5" s="128">
+        <v>199</v>
+      </c>
+      <c r="B5" s="129" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="129" t="s">
         <v>319</v>
       </c>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="108">
+      <c r="D5" s="129"/>
+      <c r="E5" s="129" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="129"/>
+      <c r="G5" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="130">
         <v>2026</v>
       </c>
       <c r="I5" s="48"/>
@@ -6008,24 +6057,24 @@
       <c r="Z5" s="90"/>
     </row>
     <row r="6" spans="1:26">
-      <c r="A6" s="65">
-        <v>197</v>
-      </c>
-      <c r="B6" s="66" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="66" t="s">
+      <c r="A6" s="106">
+        <v>198</v>
+      </c>
+      <c r="B6" s="108" t="s">
         <v>317</v>
       </c>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="66">
+      <c r="C6" s="108" t="s">
+        <v>318</v>
+      </c>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="108" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="108">
         <v>2026</v>
       </c>
       <c r="I6" s="48"/>
@@ -6048,25 +6097,25 @@
       <c r="Z6" s="90"/>
     </row>
     <row r="7" spans="1:26">
-      <c r="A7" s="107">
-        <v>196</v>
-      </c>
-      <c r="B7" s="81" t="s">
-        <v>315</v>
-      </c>
-      <c r="C7" s="81" t="s">
+      <c r="A7" s="65">
+        <v>197</v>
+      </c>
+      <c r="B7" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="66" t="s">
         <v>316</v>
       </c>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="81">
-        <v>2025</v>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="66">
+        <v>2026</v>
       </c>
       <c r="I7" s="48"/>
       <c r="J7" s="57"/>
@@ -6088,25 +6137,25 @@
       <c r="Z7" s="90"/>
     </row>
     <row r="8" spans="1:26" ht="16" thickBot="1">
-      <c r="A8" s="65">
-        <v>195</v>
-      </c>
-      <c r="B8" s="66" t="s">
-        <v>120</v>
-      </c>
-      <c r="C8" s="66" t="s">
-        <v>287</v>
-      </c>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="66">
-        <v>2026</v>
+      <c r="A8" s="107">
+        <v>196</v>
+      </c>
+      <c r="B8" s="81" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" s="81" t="s">
+        <v>315</v>
+      </c>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="81">
+        <v>2025</v>
       </c>
       <c r="I8" s="48"/>
       <c r="O8" s="87"/>
@@ -6124,19 +6173,19 @@
     </row>
     <row r="9" spans="1:26" ht="16" thickBot="1">
       <c r="A9" s="65">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B9" s="66" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>25</v>
+        <v>286</v>
       </c>
       <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E9" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="66"/>
       <c r="G9" s="66" t="s">
         <v>27</v>
       </c>
@@ -6163,24 +6212,24 @@
       <c r="Z9" s="104"/>
     </row>
     <row r="10" spans="1:26" ht="16" thickBot="1">
-      <c r="A10" s="107">
-        <v>193</v>
-      </c>
-      <c r="B10" s="81" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="81" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="81"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="81">
+      <c r="A10" s="65">
+        <v>194</v>
+      </c>
+      <c r="B10" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="66" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="66">
         <v>2026</v>
       </c>
       <c r="I10" s="48"/>
@@ -6198,25 +6247,25 @@
       <c r="U10" s="87"/>
     </row>
     <row r="11" spans="1:26" ht="16" thickBot="1">
-      <c r="A11" s="65">
-        <v>192</v>
-      </c>
-      <c r="B11" s="66" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="66" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="66" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="66">
-        <v>2025</v>
+      <c r="A11" s="107">
+        <v>193</v>
+      </c>
+      <c r="B11" s="81" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="81" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="81">
+        <v>2026</v>
       </c>
       <c r="I11" s="48"/>
       <c r="J11" s="57"/>
@@ -6239,13 +6288,13 @@
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="65">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B12" s="66" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C12" s="66" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D12" s="66"/>
       <c r="E12" s="66"/>
@@ -6279,24 +6328,24 @@
     </row>
     <row r="13" spans="1:26" ht="16" thickBot="1">
       <c r="A13" s="65">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C13" s="66" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D13" s="66"/>
-      <c r="E13" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G13" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H13" s="66">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="I13" s="48"/>
       <c r="J13" s="57"/>
@@ -6319,13 +6368,13 @@
     </row>
     <row r="14" spans="1:26" ht="16" thickBot="1">
       <c r="A14" s="65">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B14" s="66" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C14" s="66" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D14" s="66"/>
       <c r="E14" s="66" t="s">
@@ -6336,7 +6385,7 @@
         <v>27</v>
       </c>
       <c r="H14" s="66">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="I14" s="48"/>
       <c r="J14" s="77"/>
@@ -6354,18 +6403,18 @@
     </row>
     <row r="15" spans="1:26" ht="16.25" customHeight="1" thickBot="1">
       <c r="A15" s="65">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B15" s="66" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C15" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="66"/>
+        <v>42</v>
+      </c>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="F15" s="66"/>
       <c r="G15" s="66" t="s">
         <v>27</v>
@@ -6394,18 +6443,18 @@
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="65">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B16" s="66" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C16" s="66" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="D16" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="66"/>
       <c r="F16" s="66"/>
       <c r="G16" s="66" t="s">
         <v>27</v>
@@ -6434,13 +6483,13 @@
     </row>
     <row r="17" spans="1:26">
       <c r="A17" s="65">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B17" s="66" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C17" s="66" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D17" s="66"/>
       <c r="E17" s="66" t="s">
@@ -6473,24 +6522,24 @@
       <c r="Z17" s="90"/>
     </row>
     <row r="18" spans="1:26">
-      <c r="A18" s="107">
-        <v>185</v>
-      </c>
-      <c r="B18" s="81" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="81"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="81" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="H18" s="81">
+      <c r="A18" s="65">
+        <v>186</v>
+      </c>
+      <c r="B18" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="66"/>
+      <c r="G18" s="66" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="66">
         <v>2025</v>
       </c>
       <c r="I18" s="48"/>
@@ -6514,19 +6563,19 @@
     </row>
     <row r="19" spans="1:26">
       <c r="A19" s="107">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B19" s="81" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C19" s="81" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D19" s="81"/>
-      <c r="E19" s="81" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="81" t="s">
+        <v>26</v>
+      </c>
       <c r="G19" s="81" t="s">
         <v>27</v>
       </c>
@@ -6554,18 +6603,18 @@
     </row>
     <row r="20" spans="1:26">
       <c r="A20" s="107">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B20" s="81" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C20" s="81" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="81" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="81"/>
+        <v>55</v>
+      </c>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81" t="s">
+        <v>26</v>
+      </c>
       <c r="F20" s="81"/>
       <c r="G20" s="81" t="s">
         <v>27</v>
@@ -6594,18 +6643,18 @@
     </row>
     <row r="21" spans="1:26" ht="16" thickBot="1">
       <c r="A21" s="107">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B21" s="81" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="C21" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="81"/>
-      <c r="E21" s="81" t="s">
-        <v>26</v>
-      </c>
+      <c r="D21" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="81"/>
       <c r="F21" s="81"/>
       <c r="G21" s="81" t="s">
         <v>27</v>
@@ -6633,24 +6682,24 @@
       <c r="Z21" s="102"/>
     </row>
     <row r="22" spans="1:26">
-      <c r="A22" s="107">
-        <v>181</v>
-      </c>
-      <c r="B22" s="81" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="81" t="s">
+      <c r="A22" s="65">
+        <v>180</v>
+      </c>
+      <c r="B22" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="81" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="81"/>
-      <c r="F22" s="81"/>
-      <c r="G22" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="H22" s="81">
+      <c r="C22" s="66" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="66" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="66">
         <v>2025</v>
       </c>
       <c r="I22" s="48"/>
@@ -6674,13 +6723,13 @@
     </row>
     <row r="23" spans="1:26">
       <c r="A23" s="65">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B23" s="66" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="66" t="s">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="C23" s="66">
+        <v>900</v>
       </c>
       <c r="D23" s="66"/>
       <c r="E23" s="66"/>
@@ -6714,19 +6763,19 @@
     </row>
     <row r="24" spans="1:26">
       <c r="A24" s="65">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B24" s="66" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="66">
-        <v>900</v>
+      <c r="C24" s="66" t="s">
+        <v>65</v>
       </c>
       <c r="D24" s="66"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E24" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="66"/>
       <c r="G24" s="66" t="s">
         <v>27</v>
       </c>
@@ -6753,18 +6802,18 @@
     </row>
     <row r="25" spans="1:26" ht="16" thickBot="1">
       <c r="A25" s="65">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B25" s="66" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C25" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="D25" s="66"/>
-      <c r="E25" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="D25" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="66"/>
       <c r="F25" s="66"/>
       <c r="G25" s="66" t="s">
         <v>27</v>
@@ -6793,19 +6842,19 @@
     </row>
     <row r="26" spans="1:26">
       <c r="A26" s="65">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B26" s="66" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="C26" s="66" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="D26" s="66"/>
       <c r="E26" s="66"/>
-      <c r="F26" s="66"/>
+      <c r="F26" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G26" s="66" t="s">
         <v>27</v>
       </c>
@@ -6833,19 +6882,19 @@
     </row>
     <row r="27" spans="1:26" ht="16.25" customHeight="1">
       <c r="A27" s="65">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B27" s="66" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C27" s="66" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" s="66"/>
+        <v>70</v>
+      </c>
+      <c r="D27" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E27" s="66"/>
-      <c r="F27" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F27" s="66"/>
       <c r="G27" s="66" t="s">
         <v>27</v>
       </c>
@@ -6873,13 +6922,13 @@
     </row>
     <row r="28" spans="1:26">
       <c r="A28" s="65">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" s="66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D28" s="66" t="s">
         <v>26</v>
@@ -6913,13 +6962,13 @@
     </row>
     <row r="29" spans="1:26">
       <c r="A29" s="65">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B29" s="66" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" s="66" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D29" s="66" t="s">
         <v>26</v>
@@ -6953,19 +7002,19 @@
     </row>
     <row r="30" spans="1:26">
       <c r="A30" s="65">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B30" s="66" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C30" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="D30" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="D30" s="66"/>
       <c r="E30" s="66"/>
-      <c r="F30" s="66"/>
+      <c r="F30" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G30" s="66" t="s">
         <v>27</v>
       </c>
@@ -6993,24 +7042,24 @@
     </row>
     <row r="31" spans="1:26">
       <c r="A31" s="65">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B31" s="66" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C31" s="66" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D31" s="66"/>
-      <c r="E31" s="66"/>
-      <c r="F31" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E31" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F31" s="66"/>
       <c r="G31" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H31" s="66">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="I31" s="48"/>
       <c r="J31" s="58"/>
@@ -7033,24 +7082,24 @@
     </row>
     <row r="32" spans="1:26">
       <c r="A32" s="65">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B32" s="66" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C32" s="66" t="s">
-        <v>78</v>
-      </c>
-      <c r="D32" s="66"/>
-      <c r="E32" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="D32" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="66"/>
       <c r="F32" s="66"/>
       <c r="G32" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H32" s="66">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="I32" s="48"/>
       <c r="J32" s="58"/>
@@ -7073,24 +7122,24 @@
     </row>
     <row r="33" spans="1:26">
       <c r="A33" s="65">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B33" s="66" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" s="66" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" s="66"/>
+        <v>81</v>
+      </c>
+      <c r="D33" s="66"/>
+      <c r="E33" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="F33" s="66"/>
       <c r="G33" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H33" s="66">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="I33" s="48"/>
       <c r="J33" s="58"/>
@@ -7113,24 +7162,24 @@
     </row>
     <row r="34" spans="1:26">
       <c r="A34" s="65">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B34" s="66" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34" s="66" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D34" s="66"/>
-      <c r="E34" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F34" s="66"/>
+      <c r="E34" s="66"/>
+      <c r="F34" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G34" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H34" s="66">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="I34" s="48"/>
       <c r="J34" s="58"/>
@@ -7153,19 +7202,19 @@
     </row>
     <row r="35" spans="1:26">
       <c r="A35" s="65">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B35" s="66" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C35" s="66" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="66"/>
+      <c r="D35" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E35" s="66"/>
-      <c r="F35" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F35" s="66"/>
       <c r="G35" s="66" t="s">
         <v>27</v>
       </c>
@@ -7193,24 +7242,24 @@
     </row>
     <row r="36" spans="1:26">
       <c r="A36" s="65">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B36" s="66" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="C36" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="D36" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="D36" s="66"/>
       <c r="E36" s="66"/>
-      <c r="F36" s="66"/>
+      <c r="F36" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G36" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H36" s="66">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="I36" s="48"/>
       <c r="J36" s="58"/>
@@ -7233,24 +7282,24 @@
     </row>
     <row r="37" spans="1:26">
       <c r="A37" s="65">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B37" s="66" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="C37" s="66" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D37" s="66"/>
-      <c r="E37" s="66"/>
-      <c r="F37" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E37" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F37" s="66"/>
       <c r="G37" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H37" s="66">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="I37" s="48"/>
       <c r="J37" s="58"/>
@@ -7273,24 +7322,24 @@
     </row>
     <row r="38" spans="1:26">
       <c r="A38" s="65">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B38" s="66" t="s">
-        <v>87</v>
-      </c>
-      <c r="C38" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="D38" s="66"/>
-      <c r="E38" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="C38" s="66">
+        <v>4</v>
+      </c>
+      <c r="D38" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E38" s="66"/>
       <c r="F38" s="66"/>
       <c r="G38" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H38" s="66">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="I38" s="48"/>
       <c r="J38" s="58"/>
@@ -7313,24 +7362,24 @@
     </row>
     <row r="39" spans="1:26">
       <c r="A39" s="65">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B39" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="C39" s="66">
-        <v>4</v>
-      </c>
-      <c r="D39" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="C39" s="66" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39" s="66"/>
       <c r="E39" s="66"/>
-      <c r="F39" s="66"/>
+      <c r="F39" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G39" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H39" s="66">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="I39" s="48"/>
       <c r="J39" s="58"/>
@@ -7353,24 +7402,24 @@
     </row>
     <row r="40" spans="1:26">
       <c r="A40" s="65">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B40" s="66" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="C40" s="66" t="s">
         <v>91</v>
       </c>
       <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E40" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F40" s="66"/>
       <c r="G40" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H40" s="66">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="I40" s="48"/>
       <c r="J40" s="58"/>
@@ -7393,24 +7442,24 @@
     </row>
     <row r="41" spans="1:26">
       <c r="A41" s="65">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B41" s="66" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C41" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="D41" s="66"/>
-      <c r="E41" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="D41" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" s="66"/>
       <c r="F41" s="66"/>
       <c r="G41" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H41" s="66">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="I41" s="48"/>
       <c r="J41" s="58"/>
@@ -7433,19 +7482,19 @@
     </row>
     <row r="42" spans="1:26">
       <c r="A42" s="65">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B42" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C42" s="66" t="s">
         <v>93</v>
       </c>
-      <c r="D42" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="D42" s="66"/>
       <c r="E42" s="66"/>
-      <c r="F42" s="66"/>
+      <c r="F42" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G42" s="66" t="s">
         <v>27</v>
       </c>
@@ -7473,19 +7522,19 @@
     </row>
     <row r="43" spans="1:26">
       <c r="A43" s="65">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="66" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="C43" s="66" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D43" s="66"/>
-      <c r="E43" s="66"/>
-      <c r="F43" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E43" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F43" s="66"/>
       <c r="G43" s="66" t="s">
         <v>27</v>
       </c>
@@ -7513,18 +7562,18 @@
     </row>
     <row r="44" spans="1:26">
       <c r="A44" s="65">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B44" s="66" t="s">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="C44" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="66"/>
-      <c r="E44" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="D44" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" s="66"/>
       <c r="F44" s="66"/>
       <c r="G44" s="66" t="s">
         <v>27</v>
@@ -7553,19 +7602,19 @@
     </row>
     <row r="45" spans="1:26">
       <c r="A45" s="65">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B45" s="66" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="C45" s="66" t="s">
-        <v>97</v>
-      </c>
-      <c r="D45" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="D45" s="66"/>
       <c r="E45" s="66"/>
-      <c r="F45" s="66"/>
+      <c r="F45" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G45" s="66" t="s">
         <v>27</v>
       </c>
@@ -7593,19 +7642,19 @@
     </row>
     <row r="46" spans="1:26">
       <c r="A46" s="65">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B46" s="66" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="C46" s="66" t="s">
         <v>99</v>
       </c>
       <c r="D46" s="66"/>
-      <c r="E46" s="66"/>
-      <c r="F46" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E46" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F46" s="66"/>
       <c r="G46" s="66" t="s">
         <v>27</v>
       </c>
@@ -7633,18 +7682,18 @@
     </row>
     <row r="47" spans="1:26">
       <c r="A47" s="65">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B47" s="66" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="C47" s="66" t="s">
-        <v>100</v>
-      </c>
-      <c r="D47" s="66"/>
-      <c r="E47" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="D47" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E47" s="66"/>
       <c r="F47" s="66"/>
       <c r="G47" s="66" t="s">
         <v>27</v>
@@ -7673,19 +7722,19 @@
     </row>
     <row r="48" spans="1:26">
       <c r="A48" s="65">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B48" s="66" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C48" s="66" t="s">
-        <v>102</v>
-      </c>
-      <c r="D48" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="D48" s="66"/>
       <c r="E48" s="66"/>
-      <c r="F48" s="66"/>
+      <c r="F48" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G48" s="66" t="s">
         <v>27</v>
       </c>
@@ -7713,19 +7762,19 @@
     </row>
     <row r="49" spans="1:26">
       <c r="A49" s="65">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B49" s="66" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="C49" s="66" t="s">
         <v>104</v>
       </c>
       <c r="D49" s="66"/>
-      <c r="E49" s="66"/>
-      <c r="F49" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E49" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F49" s="66"/>
       <c r="G49" s="66" t="s">
         <v>27</v>
       </c>
@@ -7753,24 +7802,24 @@
     </row>
     <row r="50" spans="1:26">
       <c r="A50" s="65">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B50" s="66" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="C50" s="66" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D50" s="66"/>
-      <c r="E50" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F50" s="66"/>
+      <c r="E50" s="66"/>
+      <c r="F50" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G50" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H50" s="66">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="I50" s="48"/>
       <c r="J50" s="58"/>
@@ -7793,24 +7842,24 @@
     </row>
     <row r="51" spans="1:26">
       <c r="A51" s="65">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B51" s="66" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C51" s="66" t="s">
-        <v>107</v>
-      </c>
-      <c r="D51" s="66"/>
+        <v>108</v>
+      </c>
+      <c r="D51" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E51" s="66"/>
-      <c r="F51" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F51" s="66"/>
       <c r="G51" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H51" s="66">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="I51" s="48"/>
       <c r="J51" s="58"/>
@@ -7833,13 +7882,13 @@
     </row>
     <row r="52" spans="1:26">
       <c r="A52" s="65">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B52" s="66" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C52" s="66" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D52" s="66" t="s">
         <v>26</v>
@@ -7850,7 +7899,7 @@
         <v>27</v>
       </c>
       <c r="H52" s="66">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="I52" s="48"/>
       <c r="J52" s="58"/>
@@ -7873,24 +7922,24 @@
     </row>
     <row r="53" spans="1:26">
       <c r="A53" s="65">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B53" s="66" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C53" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="D53" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="D53" s="66"/>
       <c r="E53" s="66"/>
-      <c r="F53" s="66"/>
+      <c r="F53" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G53" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H53" s="66">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="I53" s="48"/>
       <c r="J53" s="58"/>
@@ -7913,19 +7962,19 @@
     </row>
     <row r="54" spans="1:26">
       <c r="A54" s="65">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B54" s="66" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C54" s="66" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D54" s="66"/>
-      <c r="E54" s="66"/>
-      <c r="F54" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E54" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F54" s="66"/>
       <c r="G54" s="66" t="s">
         <v>27</v>
       </c>
@@ -7953,24 +8002,24 @@
     </row>
     <row r="55" spans="1:26">
       <c r="A55" s="65">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B55" s="66" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C55" s="66" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D55" s="66"/>
-      <c r="E55" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F55" s="66"/>
+      <c r="E55" s="66"/>
+      <c r="F55" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G55" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H55" s="66">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="I55" s="48"/>
       <c r="J55" s="58"/>
@@ -7993,24 +8042,24 @@
     </row>
     <row r="56" spans="1:26">
       <c r="A56" s="65">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B56" s="66" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C56" s="66" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D56" s="66"/>
-      <c r="E56" s="66"/>
-      <c r="F56" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E56" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F56" s="66"/>
       <c r="G56" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H56" s="66">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="I56" s="48"/>
       <c r="J56" s="58"/>
@@ -8033,13 +8082,13 @@
     </row>
     <row r="57" spans="1:26">
       <c r="A57" s="65">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B57" s="66" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C57" s="66" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D57" s="66"/>
       <c r="E57" s="66" t="s">
@@ -8073,18 +8122,18 @@
     </row>
     <row r="58" spans="1:26" ht="16" thickBot="1">
       <c r="A58" s="65">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B58" s="66" t="s">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="C58" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="D58" s="66"/>
-      <c r="E58" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="D58" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58" s="66"/>
       <c r="F58" s="66"/>
       <c r="G58" s="66" t="s">
         <v>27</v>
@@ -8113,24 +8162,24 @@
     </row>
     <row r="59" spans="1:26">
       <c r="A59" s="65">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B59" s="66" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C59" s="66" t="s">
         <v>122</v>
       </c>
-      <c r="D59" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="D59" s="66"/>
       <c r="E59" s="66"/>
-      <c r="F59" s="66"/>
+      <c r="F59" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G59" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H59" s="66">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="I59" s="48"/>
       <c r="S59"/>
@@ -8144,10 +8193,10 @@
     </row>
     <row r="60" spans="1:26" ht="16" thickBot="1">
       <c r="A60" s="65">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B60" s="66" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="C60" s="66" t="s">
         <v>123</v>
@@ -8172,82 +8221,82 @@
     </row>
     <row r="61" spans="1:26">
       <c r="A61" s="65">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B61" s="66" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="C61" s="66" t="s">
-        <v>124</v>
-      </c>
-      <c r="D61" s="66"/>
+        <v>125</v>
+      </c>
+      <c r="D61" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E61" s="66"/>
-      <c r="F61" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F61" s="66"/>
       <c r="G61" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H61" s="66">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="I61" s="48"/>
     </row>
     <row r="62" spans="1:26">
       <c r="A62" s="65">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B62" s="66" t="s">
-        <v>125</v>
+        <v>35</v>
       </c>
       <c r="C62" s="66" t="s">
         <v>126</v>
       </c>
-      <c r="D62" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="D62" s="66"/>
       <c r="E62" s="66"/>
-      <c r="F62" s="66"/>
+      <c r="F62" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G62" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H62" s="66">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="I62" s="48"/>
     </row>
     <row r="63" spans="1:26">
       <c r="A63" s="65">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B63" s="66" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="C63" s="66" t="s">
-        <v>127</v>
-      </c>
-      <c r="D63" s="66"/>
+        <v>128</v>
+      </c>
+      <c r="D63" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E63" s="66"/>
-      <c r="F63" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F63" s="66"/>
       <c r="G63" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H63" s="66">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="I63" s="48"/>
     </row>
     <row r="64" spans="1:26">
       <c r="A64" s="65">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B64" s="66" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C64" s="66" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D64" s="66" t="s">
         <v>26</v>
@@ -8258,19 +8307,19 @@
         <v>27</v>
       </c>
       <c r="H64" s="66">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="I64" s="48"/>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="65">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B65" s="66" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C65" s="66" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D65" s="66" t="s">
         <v>26</v>
@@ -8281,24 +8330,24 @@
         <v>27</v>
       </c>
       <c r="H65" s="66">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="I65" s="48"/>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="65">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B66" s="66" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C66" s="66" t="s">
-        <v>133</v>
-      </c>
-      <c r="D66" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="E66" s="66"/>
+        <v>134</v>
+      </c>
+      <c r="D66" s="66"/>
+      <c r="E66" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="F66" s="66"/>
       <c r="G66" s="66" t="s">
         <v>27</v>
@@ -8310,10 +8359,10 @@
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="65">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B67" s="66" t="s">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="C67" s="66" t="s">
         <v>135</v>
@@ -8333,19 +8382,19 @@
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="65">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B68" s="66" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C68" s="66" t="s">
         <v>136</v>
       </c>
       <c r="D68" s="66"/>
-      <c r="E68" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F68" s="66"/>
+      <c r="E68" s="66"/>
+      <c r="F68" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G68" s="66" t="s">
         <v>27</v>
       </c>
@@ -8356,19 +8405,19 @@
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="65">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B69" s="66" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C69" s="66" t="s">
         <v>137</v>
       </c>
-      <c r="D69" s="66"/>
+      <c r="D69" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E69" s="66"/>
-      <c r="F69" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F69" s="66"/>
       <c r="G69" s="66" t="s">
         <v>27</v>
       </c>
@@ -8379,42 +8428,42 @@
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="65">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B70" s="66" t="s">
-        <v>43</v>
-      </c>
-      <c r="C70" s="66" t="s">
         <v>138</v>
       </c>
-      <c r="D70" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="C70" s="66">
+        <v>12</v>
+      </c>
+      <c r="D70" s="66"/>
       <c r="E70" s="66"/>
-      <c r="F70" s="66"/>
+      <c r="F70" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G70" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H70" s="66">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="I70" s="48"/>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="65">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B71" s="66" t="s">
         <v>139</v>
       </c>
-      <c r="C71" s="66">
-        <v>12</v>
+      <c r="C71" s="66" t="s">
+        <v>140</v>
       </c>
       <c r="D71" s="66"/>
-      <c r="E71" s="66"/>
-      <c r="F71" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E71" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F71" s="66"/>
       <c r="G71" s="66" t="s">
         <v>27</v>
       </c>
@@ -8425,88 +8474,88 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="65">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B72" s="66" t="s">
-        <v>140</v>
-      </c>
-      <c r="C72" s="66" t="s">
+        <v>38</v>
+      </c>
+      <c r="C72" s="69" t="s">
         <v>141</v>
       </c>
       <c r="D72" s="66"/>
-      <c r="E72" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F72" s="66"/>
+      <c r="E72" s="66"/>
+      <c r="F72" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G72" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H72" s="66">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="I72" s="48"/>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="65">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B73" s="66" t="s">
-        <v>38</v>
-      </c>
-      <c r="C73" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="C73" s="66" t="s">
         <v>142</v>
       </c>
-      <c r="D73" s="66"/>
+      <c r="D73" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E73" s="66"/>
-      <c r="F73" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F73" s="66"/>
       <c r="G73" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H73" s="66">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="I73" s="48"/>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="65">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B74" s="66" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="C74" s="66" t="s">
-        <v>143</v>
-      </c>
-      <c r="D74" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="D74" s="66"/>
       <c r="E74" s="66"/>
-      <c r="F74" s="66"/>
+      <c r="F74" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G74" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H74" s="66">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="I74" s="48"/>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="65">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B75" s="66" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C75" s="66" t="s">
-        <v>145</v>
-      </c>
-      <c r="D75" s="66"/>
+        <v>146</v>
+      </c>
+      <c r="D75" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E75" s="66"/>
-      <c r="F75" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F75" s="66"/>
       <c r="G75" s="66" t="s">
         <v>27</v>
       </c>
@@ -8517,19 +8566,19 @@
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="65">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B76" s="66" t="s">
-        <v>146</v>
-      </c>
-      <c r="C76" s="66" t="s">
-        <v>147</v>
-      </c>
-      <c r="D76" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="C76" s="66">
+        <v>8</v>
+      </c>
+      <c r="D76" s="66"/>
       <c r="E76" s="66"/>
-      <c r="F76" s="66"/>
+      <c r="F76" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G76" s="66" t="s">
         <v>27</v>
       </c>
@@ -8540,63 +8589,63 @@
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="65">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B77" s="66" t="s">
-        <v>64</v>
-      </c>
-      <c r="C77" s="66">
-        <v>8</v>
-      </c>
-      <c r="D77" s="66"/>
+        <v>147</v>
+      </c>
+      <c r="C77" s="66" t="s">
+        <v>148</v>
+      </c>
+      <c r="D77" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E77" s="66"/>
-      <c r="F77" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F77" s="66"/>
       <c r="G77" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H77" s="66">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="I77" s="48"/>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="65">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B78" s="66" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C78" s="66" t="s">
-        <v>149</v>
-      </c>
-      <c r="D78" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="D78" s="66"/>
       <c r="E78" s="66"/>
       <c r="F78" s="66"/>
       <c r="G78" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H78" s="66">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="I78" s="48"/>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="65">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B79" s="66" t="s">
-        <v>150</v>
-      </c>
-      <c r="C79" s="66" t="s">
         <v>151</v>
+      </c>
+      <c r="C79" s="66">
+        <v>1</v>
       </c>
       <c r="D79" s="66"/>
       <c r="E79" s="66"/>
-      <c r="F79" s="66"/>
+      <c r="F79" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G79" s="66" t="s">
         <v>27</v>
       </c>
@@ -8607,13 +8656,13 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="65">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B80" s="66" t="s">
         <v>152</v>
       </c>
-      <c r="C80" s="66">
-        <v>1</v>
+      <c r="C80" s="66" t="s">
+        <v>153</v>
       </c>
       <c r="D80" s="66"/>
       <c r="E80" s="66"/>
@@ -8630,13 +8679,13 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="65">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B81" s="66" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C81" s="66" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D81" s="66"/>
       <c r="E81" s="66"/>
@@ -8653,65 +8702,65 @@
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="65">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B82" s="66" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="C82" s="66" t="s">
         <v>156</v>
       </c>
       <c r="D82" s="66"/>
-      <c r="E82" s="66"/>
-      <c r="F82" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E82" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F82" s="66"/>
       <c r="G82" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H82" s="66">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="I82" s="48"/>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="65">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B83" s="66" t="s">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="C83" s="66" t="s">
-        <v>157</v>
-      </c>
-      <c r="D83" s="66"/>
-      <c r="E83" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="D83" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E83" s="66"/>
       <c r="F83" s="66"/>
       <c r="G83" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H83" s="66">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="I83" s="48"/>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="65">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B84" s="66" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C84" s="66" t="s">
-        <v>159</v>
-      </c>
-      <c r="D84" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="D84" s="66"/>
       <c r="E84" s="66"/>
-      <c r="F84" s="66"/>
+      <c r="F84" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G84" s="66" t="s">
         <v>27</v>
       </c>
@@ -8722,33 +8771,33 @@
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="65">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B85" s="66" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C85" s="66" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D85" s="66"/>
-      <c r="E85" s="66"/>
-      <c r="F85" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E85" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F85" s="66"/>
       <c r="G85" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H85" s="66">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="I85" s="48"/>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="65">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B86" s="66" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="C86" s="66" t="s">
         <v>163</v>
@@ -8762,40 +8811,40 @@
         <v>27</v>
       </c>
       <c r="H86" s="66">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="65">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B87" s="66" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="C87" s="66" t="s">
         <v>164</v>
       </c>
       <c r="D87" s="66"/>
-      <c r="E87" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F87" s="66"/>
+      <c r="E87" s="66"/>
+      <c r="F87" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G87" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H87" s="66">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="65">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B88" s="66" t="s">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="C88" s="66" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D88" s="66"/>
       <c r="E88" s="66"/>
@@ -8811,63 +8860,63 @@
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="65">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B89" s="66" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="C89" s="66" t="s">
         <v>167</v>
       </c>
-      <c r="D89" s="66"/>
+      <c r="D89" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E89" s="66"/>
-      <c r="F89" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F89" s="66"/>
       <c r="G89" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H89" s="66">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="65">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B90" s="66" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C90" s="66" t="s">
-        <v>168</v>
-      </c>
-      <c r="D90" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="E90" s="66"/>
+        <v>169</v>
+      </c>
+      <c r="D90" s="66"/>
+      <c r="E90" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="F90" s="66"/>
       <c r="G90" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H90" s="66">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="65">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B91" s="66" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C91" s="66" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D91" s="66"/>
-      <c r="E91" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F91" s="66"/>
+      <c r="E91" s="66"/>
+      <c r="F91" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G91" s="66" t="s">
         <v>27</v>
       </c>
@@ -8877,19 +8926,19 @@
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="65">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B92" s="66" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C92" s="66" t="s">
-        <v>172</v>
-      </c>
-      <c r="D92" s="66"/>
+        <v>173</v>
+      </c>
+      <c r="D92" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E92" s="66"/>
-      <c r="F92" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F92" s="66"/>
       <c r="G92" s="66" t="s">
         <v>27</v>
       </c>
@@ -8899,19 +8948,19 @@
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="65">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B93" s="66" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C93" s="66" t="s">
-        <v>174</v>
-      </c>
-      <c r="D93" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="D93" s="66"/>
       <c r="E93" s="66"/>
-      <c r="F93" s="66"/>
+      <c r="F93" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G93" s="66" t="s">
         <v>27</v>
       </c>
@@ -8921,19 +8970,19 @@
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="65">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B94" s="66" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C94" s="66" t="s">
-        <v>176</v>
-      </c>
-      <c r="D94" s="66"/>
+        <v>177</v>
+      </c>
+      <c r="D94" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E94" s="66"/>
-      <c r="F94" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F94" s="66"/>
       <c r="G94" s="66" t="s">
         <v>27</v>
       </c>
@@ -8943,18 +8992,18 @@
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="65">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B95" s="66" t="s">
-        <v>177</v>
+        <v>48</v>
       </c>
       <c r="C95" s="66" t="s">
         <v>178</v>
       </c>
-      <c r="D95" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="E95" s="66"/>
+      <c r="D95" s="66"/>
+      <c r="E95" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="F95" s="66"/>
       <c r="G95" s="66" t="s">
         <v>27</v>
@@ -8965,18 +9014,18 @@
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="65">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B96" s="66" t="s">
-        <v>48</v>
+        <v>179</v>
       </c>
       <c r="C96" s="66" t="s">
-        <v>179</v>
-      </c>
-      <c r="D96" s="66"/>
-      <c r="E96" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="D96" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E96" s="66"/>
       <c r="F96" s="66"/>
       <c r="G96" s="66" t="s">
         <v>27</v>
@@ -8987,63 +9036,63 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="65">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B97" s="66" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C97" s="66" t="s">
-        <v>181</v>
-      </c>
-      <c r="D97" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="D97" s="66"/>
       <c r="E97" s="66"/>
-      <c r="F97" s="66"/>
+      <c r="F97" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G97" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H97" s="66">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="65">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B98" s="66" t="s">
-        <v>182</v>
+        <v>127</v>
       </c>
       <c r="C98" s="66" t="s">
         <v>183</v>
       </c>
       <c r="D98" s="66"/>
-      <c r="E98" s="66"/>
-      <c r="F98" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E98" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F98" s="66"/>
       <c r="G98" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H98" s="66">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="65">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B99" s="66" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="C99" s="66" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D99" s="66"/>
-      <c r="E99" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F99" s="66"/>
+      <c r="E99" s="66"/>
+      <c r="F99" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G99" s="66" t="s">
         <v>27</v>
       </c>
@@ -9053,13 +9102,13 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="65">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B100" s="66" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C100" s="66" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D100" s="66"/>
       <c r="E100" s="66"/>
@@ -9075,19 +9124,19 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="65">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B101" s="66" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C101" s="66" t="s">
-        <v>188</v>
-      </c>
-      <c r="D101" s="66"/>
+        <v>189</v>
+      </c>
+      <c r="D101" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E101" s="66"/>
-      <c r="F101" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F101" s="66"/>
       <c r="G101" s="66" t="s">
         <v>27</v>
       </c>
@@ -9097,10 +9146,10 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="65">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B102" s="66" t="s">
-        <v>189</v>
+        <v>56</v>
       </c>
       <c r="C102" s="66" t="s">
         <v>190</v>
@@ -9119,32 +9168,32 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="65">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B103" s="66" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C103" s="66" t="s">
         <v>191</v>
       </c>
-      <c r="D103" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="E103" s="66"/>
+      <c r="D103" s="66"/>
+      <c r="E103" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="F103" s="66"/>
       <c r="G103" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H103" s="66">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="65">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B104" s="66" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C104" s="66" t="s">
         <v>192</v>
@@ -9163,35 +9212,35 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="65">
-        <v>98</v>
-      </c>
-      <c r="B105" s="66" t="s">
-        <v>95</v>
-      </c>
-      <c r="C105" s="66" t="s">
+        <v>97</v>
+      </c>
+      <c r="B105" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="D105" s="66"/>
-      <c r="E105" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F105" s="66"/>
-      <c r="G105" s="66" t="s">
-        <v>27</v>
-      </c>
-      <c r="H105" s="66">
-        <v>2022</v>
+      <c r="C105" s="81" t="s">
+        <v>194</v>
+      </c>
+      <c r="D105" s="81"/>
+      <c r="E105" s="81"/>
+      <c r="F105" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="G105" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="H105" s="81">
+        <v>2023</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="65">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B106" s="81" t="s">
-        <v>194</v>
-      </c>
-      <c r="C106" s="81" t="s">
-        <v>195</v>
+        <v>138</v>
+      </c>
+      <c r="C106" s="81">
+        <v>11</v>
       </c>
       <c r="D106" s="81"/>
       <c r="E106" s="81"/>
@@ -9202,134 +9251,134 @@
         <v>27</v>
       </c>
       <c r="H106" s="81">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="65">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B107" s="81" t="s">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="C107" s="81">
-        <v>11</v>
-      </c>
-      <c r="D107" s="81"/>
+        <v>408</v>
+      </c>
+      <c r="D107" s="81" t="s">
+        <v>26</v>
+      </c>
       <c r="E107" s="81"/>
-      <c r="F107" s="81" t="s">
-        <v>26</v>
-      </c>
+      <c r="F107" s="81"/>
       <c r="G107" s="81" t="s">
         <v>27</v>
       </c>
       <c r="H107" s="81">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="65">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B108" s="81" t="s">
         <v>196</v>
       </c>
-      <c r="C108" s="81">
-        <v>408</v>
-      </c>
-      <c r="D108" s="81" t="s">
-        <v>26</v>
-      </c>
+      <c r="C108" s="81" t="s">
+        <v>197</v>
+      </c>
+      <c r="D108" s="81"/>
       <c r="E108" s="81"/>
-      <c r="F108" s="81"/>
+      <c r="F108" s="81" t="s">
+        <v>26</v>
+      </c>
       <c r="G108" s="81" t="s">
         <v>27</v>
       </c>
       <c r="H108" s="81">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="65">
-        <v>94</v>
-      </c>
-      <c r="B109" s="81" t="s">
-        <v>197</v>
-      </c>
-      <c r="C109" s="81" t="s">
+        <v>93</v>
+      </c>
+      <c r="B109" s="66" t="s">
+        <v>49</v>
+      </c>
+      <c r="C109" s="66" t="s">
         <v>198</v>
       </c>
-      <c r="D109" s="81"/>
-      <c r="E109" s="81"/>
-      <c r="F109" s="81" t="s">
-        <v>26</v>
-      </c>
-      <c r="G109" s="81" t="s">
-        <v>27</v>
-      </c>
-      <c r="H109" s="81">
+      <c r="D109" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E109" s="66"/>
+      <c r="F109" s="66"/>
+      <c r="G109" s="66" t="s">
+        <v>27</v>
+      </c>
+      <c r="H109" s="66">
         <v>2022</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="65">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B110" s="66" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C110" s="66" t="s">
         <v>199</v>
       </c>
-      <c r="D110" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="E110" s="66"/>
+      <c r="D110" s="66"/>
+      <c r="E110" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="F110" s="66"/>
       <c r="G110" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H110" s="66">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="65">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B111" s="66" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="C111" s="66" t="s">
         <v>200</v>
       </c>
       <c r="D111" s="66"/>
-      <c r="E111" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F111" s="66"/>
+      <c r="E111" s="66"/>
+      <c r="F111" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G111" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H111" s="66">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="65">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B112" s="66" t="s">
-        <v>98</v>
+        <v>201</v>
       </c>
       <c r="C112" s="66" t="s">
-        <v>201</v>
-      </c>
-      <c r="D112" s="66"/>
+        <v>202</v>
+      </c>
+      <c r="D112" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E112" s="66"/>
-      <c r="F112" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F112" s="66"/>
       <c r="G112" s="66" t="s">
         <v>27</v>
       </c>
@@ -9339,19 +9388,19 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="65">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B113" s="66" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C113" s="66" t="s">
-        <v>203</v>
-      </c>
-      <c r="D113" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="D113" s="66"/>
       <c r="E113" s="66"/>
-      <c r="F113" s="66"/>
+      <c r="F113" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G113" s="66" t="s">
         <v>27</v>
       </c>
@@ -9361,19 +9410,19 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="65">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B114" s="66" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="C114" s="66" t="s">
         <v>205</v>
       </c>
       <c r="D114" s="66"/>
-      <c r="E114" s="66"/>
-      <c r="F114" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E114" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F114" s="66"/>
       <c r="G114" s="66" t="s">
         <v>27</v>
       </c>
@@ -9383,18 +9432,18 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="65">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B115" s="66" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C115" s="66" t="s">
         <v>206</v>
       </c>
-      <c r="D115" s="66"/>
-      <c r="E115" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="D115" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E115" s="66"/>
       <c r="F115" s="66"/>
       <c r="G115" s="66" t="s">
         <v>27</v>
@@ -9405,10 +9454,10 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="65">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B116" s="66" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="C116" s="66" t="s">
         <v>207</v>
@@ -9427,19 +9476,19 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="65">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B117" s="66" t="s">
-        <v>72</v>
+        <v>208</v>
       </c>
       <c r="C117" s="66" t="s">
-        <v>208</v>
-      </c>
-      <c r="D117" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="D117" s="66"/>
       <c r="E117" s="66"/>
-      <c r="F117" s="66"/>
+      <c r="F117" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G117" s="66" t="s">
         <v>27</v>
       </c>
@@ -9449,19 +9498,19 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="65">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B118" s="66" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C118" s="66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D118" s="66"/>
-      <c r="E118" s="66"/>
-      <c r="F118" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E118" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F118" s="66"/>
       <c r="G118" s="66" t="s">
         <v>27</v>
       </c>
@@ -9471,10 +9520,10 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="65">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B119" s="66" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="C119" s="66" t="s">
         <v>212</v>
@@ -9493,13 +9542,13 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="65">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B120" s="66" t="s">
-        <v>162</v>
+        <v>213</v>
       </c>
       <c r="C120" s="66" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D120" s="66"/>
       <c r="E120" s="66" t="s">
@@ -9515,13 +9564,13 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="65">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B121" s="66" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C121" s="66" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D121" s="66"/>
       <c r="E121" s="66" t="s">
@@ -9537,19 +9586,19 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="65">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B122" s="66" t="s">
-        <v>216</v>
+        <v>33</v>
       </c>
       <c r="C122" s="66" t="s">
         <v>217</v>
       </c>
       <c r="D122" s="66"/>
-      <c r="E122" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F122" s="66"/>
+      <c r="E122" s="66"/>
+      <c r="F122" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G122" s="66" t="s">
         <v>27</v>
       </c>
@@ -9559,19 +9608,19 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="65">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B123" s="66" t="s">
-        <v>33</v>
+        <v>218</v>
       </c>
       <c r="C123" s="66" t="s">
-        <v>218</v>
-      </c>
-      <c r="D123" s="66"/>
+        <v>219</v>
+      </c>
+      <c r="D123" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E123" s="66"/>
-      <c r="F123" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F123" s="66"/>
       <c r="G123" s="66" t="s">
         <v>27</v>
       </c>
@@ -9581,19 +9630,19 @@
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="65">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B124" s="66" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C124" s="66" t="s">
-        <v>220</v>
-      </c>
-      <c r="D124" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="D124" s="66"/>
       <c r="E124" s="66"/>
-      <c r="F124" s="66"/>
+      <c r="F124" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G124" s="66" t="s">
         <v>27</v>
       </c>
@@ -9603,13 +9652,13 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="65">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B125" s="66" t="s">
-        <v>221</v>
-      </c>
-      <c r="C125" s="66" t="s">
-        <v>222</v>
+        <v>38</v>
+      </c>
+      <c r="C125" s="66">
+        <v>1</v>
       </c>
       <c r="D125" s="66"/>
       <c r="E125" s="66"/>
@@ -9620,68 +9669,68 @@
         <v>27</v>
       </c>
       <c r="H125" s="66">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="65">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B126" s="66" t="s">
-        <v>38</v>
-      </c>
-      <c r="C126" s="66">
-        <v>1</v>
+        <v>149</v>
+      </c>
+      <c r="C126" s="66" t="s">
+        <v>222</v>
       </c>
       <c r="D126" s="66"/>
-      <c r="E126" s="66"/>
-      <c r="F126" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E126" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F126" s="66"/>
       <c r="G126" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H126" s="66">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="65">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B127" s="66" t="s">
-        <v>150</v>
+        <v>223</v>
       </c>
       <c r="C127" s="66" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D127" s="66"/>
-      <c r="E127" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F127" s="66"/>
+      <c r="E127" s="66"/>
+      <c r="F127" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G127" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H127" s="66">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="65">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B128" s="66" t="s">
-        <v>224</v>
+        <v>39</v>
       </c>
       <c r="C128" s="66" t="s">
         <v>225</v>
       </c>
       <c r="D128" s="66"/>
-      <c r="E128" s="66"/>
-      <c r="F128" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E128" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F128" s="66"/>
       <c r="G128" s="66" t="s">
         <v>27</v>
       </c>
@@ -9691,10 +9740,10 @@
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="65">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B129" s="66" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="C129" s="66" t="s">
         <v>226</v>
@@ -9713,35 +9762,35 @@
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="65">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B130" s="66" t="s">
-        <v>77</v>
-      </c>
-      <c r="C130" s="66" t="s">
         <v>227</v>
       </c>
-      <c r="D130" s="66"/>
-      <c r="E130" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="C130" s="66">
+        <v>5</v>
+      </c>
+      <c r="D130" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E130" s="66"/>
       <c r="F130" s="66"/>
       <c r="G130" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H130" s="66">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="65">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B131" s="66" t="s">
         <v>228</v>
       </c>
-      <c r="C131" s="66">
-        <v>5</v>
+      <c r="C131" s="66" t="s">
+        <v>229</v>
       </c>
       <c r="D131" s="66" t="s">
         <v>26</v>
@@ -9757,10 +9806,10 @@
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="65">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B132" s="66" t="s">
-        <v>229</v>
+        <v>113</v>
       </c>
       <c r="C132" s="66" t="s">
         <v>230</v>
@@ -9779,41 +9828,41 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="65">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B133" s="66" t="s">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="C133" s="66" t="s">
-        <v>231</v>
-      </c>
-      <c r="D133" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D133" s="66"/>
       <c r="E133" s="66"/>
-      <c r="F133" s="66"/>
+      <c r="F133" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G133" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H133" s="66">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="65">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B134" s="66" t="s">
-        <v>155</v>
+        <v>231</v>
       </c>
       <c r="C134" s="66" t="s">
-        <v>45</v>
-      </c>
-      <c r="D134" s="66"/>
+        <v>232</v>
+      </c>
+      <c r="D134" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E134" s="66"/>
-      <c r="F134" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F134" s="66"/>
       <c r="G134" s="66" t="s">
         <v>27</v>
       </c>
@@ -9823,19 +9872,19 @@
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="65">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B135" s="66" t="s">
-        <v>232</v>
+        <v>124</v>
       </c>
       <c r="C135" s="66" t="s">
         <v>233</v>
       </c>
-      <c r="D135" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="D135" s="66"/>
       <c r="E135" s="66"/>
-      <c r="F135" s="66"/>
+      <c r="F135" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G135" s="66" t="s">
         <v>27</v>
       </c>
@@ -9845,32 +9894,32 @@
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="65">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B136" s="66" t="s">
-        <v>125</v>
+        <v>234</v>
       </c>
       <c r="C136" s="66" t="s">
-        <v>234</v>
-      </c>
-      <c r="D136" s="66"/>
+        <v>235</v>
+      </c>
+      <c r="D136" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E136" s="66"/>
-      <c r="F136" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F136" s="66"/>
       <c r="G136" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H136" s="66">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="65">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B137" s="66" t="s">
-        <v>235</v>
+        <v>43</v>
       </c>
       <c r="C137" s="66" t="s">
         <v>236</v>
@@ -9884,68 +9933,68 @@
         <v>27</v>
       </c>
       <c r="H137" s="66">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="65">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B138" s="66" t="s">
-        <v>43</v>
+        <v>237</v>
       </c>
       <c r="C138" s="66" t="s">
-        <v>237</v>
-      </c>
-      <c r="D138" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="D138" s="66"/>
       <c r="E138" s="66"/>
-      <c r="F138" s="66"/>
+      <c r="F138" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G138" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H138" s="66">
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="65">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B139" s="66" t="s">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="C139" s="66" t="s">
         <v>239</v>
       </c>
-      <c r="D139" s="66"/>
+      <c r="D139" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E139" s="66"/>
-      <c r="F139" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F139" s="66"/>
       <c r="G139" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H139" s="66">
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="65">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B140" s="66" t="s">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C140" s="66" t="s">
-        <v>240</v>
-      </c>
-      <c r="D140" s="66" t="s">
-        <v>26</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="D140" s="66"/>
       <c r="E140" s="66"/>
-      <c r="F140" s="66"/>
+      <c r="F140" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G140" s="66" t="s">
         <v>27</v>
       </c>
@@ -9955,76 +10004,76 @@
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="65">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B141" s="66" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="C141" s="66" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D141" s="66"/>
-      <c r="E141" s="66"/>
-      <c r="F141" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E141" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F141" s="66"/>
       <c r="G141" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H141" s="66">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="65">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B142" s="66" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="C142" s="66" t="s">
         <v>241</v>
       </c>
       <c r="D142" s="66"/>
-      <c r="E142" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F142" s="66"/>
+      <c r="E142" s="66"/>
+      <c r="F142" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G142" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H142" s="66">
-        <v>2022</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="65">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B143" s="66" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C143" s="66" t="s">
         <v>242</v>
       </c>
       <c r="D143" s="66"/>
-      <c r="E143" s="66"/>
-      <c r="F143" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E143" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F143" s="66"/>
       <c r="G143" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H143" s="66">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="65">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B144" s="66" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C144" s="66" t="s">
         <v>243</v>
@@ -10043,13 +10092,13 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="65">
+        <v>57</v>
+      </c>
+      <c r="B145" s="66" t="s">
+        <v>57</v>
+      </c>
+      <c r="C145" s="66" t="s">
         <v>58</v>
-      </c>
-      <c r="B145" s="66" t="s">
-        <v>53</v>
-      </c>
-      <c r="C145" s="66" t="s">
-        <v>244</v>
       </c>
       <c r="D145" s="66"/>
       <c r="E145" s="66" t="s">
@@ -10065,13 +10114,13 @@
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="65">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B146" s="66" t="s">
-        <v>58</v>
+        <v>213</v>
       </c>
       <c r="C146" s="66" t="s">
-        <v>59</v>
+        <v>244</v>
       </c>
       <c r="D146" s="66"/>
       <c r="E146" s="66" t="s">
@@ -10087,10 +10136,10 @@
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="65">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B147" s="66" t="s">
-        <v>214</v>
+        <v>46</v>
       </c>
       <c r="C147" s="66" t="s">
         <v>245</v>
@@ -10109,35 +10158,35 @@
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="65">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B148" s="66" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C148" s="66" t="s">
         <v>246</v>
       </c>
       <c r="D148" s="66"/>
-      <c r="E148" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F148" s="66"/>
+      <c r="E148" s="66"/>
+      <c r="F148" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G148" s="66" t="s">
         <v>27</v>
       </c>
       <c r="H148" s="66">
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="65">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B149" s="66" t="s">
-        <v>98</v>
+        <v>247</v>
       </c>
       <c r="C149" s="66" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D149" s="66"/>
       <c r="E149" s="66"/>
@@ -10148,18 +10197,18 @@
         <v>27</v>
       </c>
       <c r="H149" s="66">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="65">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B150" s="66" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C150" s="66" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D150" s="66"/>
       <c r="E150" s="66"/>
@@ -10175,19 +10224,19 @@
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="65">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B151" s="66" t="s">
-        <v>250</v>
+        <v>161</v>
       </c>
       <c r="C151" s="66" t="s">
         <v>251</v>
       </c>
       <c r="D151" s="66"/>
-      <c r="E151" s="66"/>
-      <c r="F151" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="E151" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F151" s="66"/>
       <c r="G151" s="66" t="s">
         <v>27</v>
       </c>
@@ -10197,10 +10246,10 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="65">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B152" s="66" t="s">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="C152" s="66" t="s">
         <v>252</v>
@@ -10219,19 +10268,19 @@
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="65">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B153" s="66" t="s">
-        <v>81</v>
+        <v>196</v>
       </c>
       <c r="C153" s="66" t="s">
         <v>253</v>
       </c>
       <c r="D153" s="66"/>
-      <c r="E153" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="F153" s="66"/>
+      <c r="E153" s="66"/>
+      <c r="F153" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="G153" s="66" t="s">
         <v>27</v>
       </c>
@@ -10241,19 +10290,19 @@
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="65">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B154" s="66" t="s">
-        <v>197</v>
+        <v>161</v>
       </c>
       <c r="C154" s="66" t="s">
         <v>254</v>
       </c>
-      <c r="D154" s="66"/>
+      <c r="D154" s="66" t="s">
+        <v>26</v>
+      </c>
       <c r="E154" s="66"/>
-      <c r="F154" s="66" t="s">
-        <v>26</v>
-      </c>
+      <c r="F154" s="66"/>
       <c r="G154" s="66" t="s">
         <v>27</v>
       </c>
@@ -10263,10 +10312,10 @@
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="65">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B155" s="66" t="s">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="C155" s="66" t="s">
         <v>255</v>
@@ -10285,13 +10334,13 @@
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="65">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B156" s="66" t="s">
-        <v>81</v>
-      </c>
-      <c r="C156" s="66" t="s">
-        <v>256</v>
+        <v>63</v>
+      </c>
+      <c r="C156" s="66">
+        <v>1</v>
       </c>
       <c r="D156" s="66" t="s">
         <v>26</v>
@@ -10307,13 +10356,13 @@
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="65">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B157" s="66" t="s">
-        <v>64</v>
-      </c>
-      <c r="C157" s="66">
-        <v>1</v>
+        <v>256</v>
+      </c>
+      <c r="C157" s="66" t="s">
+        <v>257</v>
       </c>
       <c r="D157" s="66" t="s">
         <v>26</v>
@@ -10329,10 +10378,10 @@
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="65">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B158" s="66" t="s">
-        <v>257</v>
+        <v>69</v>
       </c>
       <c r="C158" s="66" t="s">
         <v>258</v>
@@ -10351,13 +10400,13 @@
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="65">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B159" s="66" t="s">
-        <v>70</v>
+        <v>259</v>
       </c>
       <c r="C159" s="66" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D159" s="66" t="s">
         <v>26</v>
@@ -10373,13 +10422,13 @@
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="65">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B160" s="66" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C160" s="66" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D160" s="66" t="s">
         <v>26</v>
@@ -10395,13 +10444,13 @@
     </row>
     <row r="161" spans="1:8">
       <c r="A161" s="65">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B161" s="66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C161" s="66" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D161" s="66" t="s">
         <v>26</v>
@@ -10417,10 +10466,10 @@
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="65">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B162" s="66" t="s">
-        <v>264</v>
+        <v>73</v>
       </c>
       <c r="C162" s="66" t="s">
         <v>265</v>
@@ -10439,13 +10488,13 @@
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="65">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B163" s="66" t="s">
-        <v>74</v>
+        <v>266</v>
       </c>
       <c r="C163" s="66" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D163" s="66" t="s">
         <v>26</v>
@@ -10456,15 +10505,15 @@
         <v>27</v>
       </c>
       <c r="H163" s="66">
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="65">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B164" s="66" t="s">
-        <v>267</v>
+        <v>145</v>
       </c>
       <c r="C164" s="66" t="s">
         <v>268</v>
@@ -10483,13 +10532,13 @@
     </row>
     <row r="165" spans="1:8">
       <c r="A165" s="65">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B165" s="66" t="s">
-        <v>146</v>
+        <v>269</v>
       </c>
       <c r="C165" s="66" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D165" s="66" t="s">
         <v>26</v>
@@ -10505,13 +10554,13 @@
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="65">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B166" s="66" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C166" s="66" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D166" s="66" t="s">
         <v>26</v>
@@ -10527,13 +10576,13 @@
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="65">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B167" s="66" t="s">
-        <v>272</v>
-      </c>
-      <c r="C167" s="66" t="s">
-        <v>273</v>
+        <v>88</v>
+      </c>
+      <c r="C167" s="66">
+        <v>2</v>
       </c>
       <c r="D167" s="66" t="s">
         <v>26</v>
@@ -10549,13 +10598,13 @@
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="65">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B168" s="66" t="s">
-        <v>89</v>
-      </c>
-      <c r="C168" s="66">
-        <v>2</v>
+        <v>51</v>
+      </c>
+      <c r="C168" s="66" t="s">
+        <v>273</v>
       </c>
       <c r="D168" s="66" t="s">
         <v>26</v>
@@ -10571,10 +10620,10 @@
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="65">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B169" s="66" t="s">
-        <v>51</v>
+        <v>228</v>
       </c>
       <c r="C169" s="66" t="s">
         <v>274</v>
@@ -10593,10 +10642,10 @@
     </row>
     <row r="170" spans="1:8">
       <c r="A170" s="65">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B170" s="66" t="s">
-        <v>229</v>
+        <v>188</v>
       </c>
       <c r="C170" s="66" t="s">
         <v>275</v>
@@ -10615,13 +10664,13 @@
     </row>
     <row r="171" spans="1:8">
       <c r="A171" s="65">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B171" s="66" t="s">
-        <v>189</v>
+        <v>276</v>
       </c>
       <c r="C171" s="66" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D171" s="66" t="s">
         <v>26</v>
@@ -10637,13 +10686,13 @@
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="65">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B172" s="66" t="s">
-        <v>277</v>
+        <v>133</v>
       </c>
       <c r="C172" s="66" t="s">
-        <v>278</v>
+        <v>81</v>
       </c>
       <c r="D172" s="66" t="s">
         <v>26</v>
@@ -10659,13 +10708,13 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="65">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B173" s="66" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="C173" s="66" t="s">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="D173" s="66" t="s">
         <v>26</v>
@@ -10681,13 +10730,13 @@
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="65">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B174" s="66" t="s">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="C174" s="66" t="s">
-        <v>279</v>
+        <v>108</v>
       </c>
       <c r="D174" s="66" t="s">
         <v>26</v>
@@ -10703,13 +10752,13 @@
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="65">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B175" s="66" t="s">
-        <v>108</v>
+        <v>195</v>
       </c>
       <c r="C175" s="66" t="s">
-        <v>109</v>
+        <v>279</v>
       </c>
       <c r="D175" s="66" t="s">
         <v>26</v>
@@ -10725,10 +10774,10 @@
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="65">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B176" s="66" t="s">
-        <v>196</v>
+        <v>145</v>
       </c>
       <c r="C176" s="66" t="s">
         <v>280</v>
@@ -10747,13 +10796,13 @@
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="65">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B177" s="66" t="s">
-        <v>146</v>
+        <v>281</v>
       </c>
       <c r="C177" s="66" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D177" s="66" t="s">
         <v>26</v>
@@ -10769,10 +10818,10 @@
     </row>
     <row r="178" spans="1:8">
       <c r="A178" s="65">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B178" s="66" t="s">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="C178" s="66" t="s">
         <v>283</v>
@@ -10791,10 +10840,10 @@
     </row>
     <row r="179" spans="1:8">
       <c r="A179" s="65">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B179" s="66" t="s">
-        <v>257</v>
+        <v>149</v>
       </c>
       <c r="C179" s="66" t="s">
         <v>284</v>
@@ -10808,15 +10857,15 @@
         <v>27</v>
       </c>
       <c r="H179" s="66">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="65">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B180" s="66" t="s">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="C180" s="66" t="s">
         <v>285</v>
@@ -10835,10 +10884,10 @@
     </row>
     <row r="181" spans="1:8">
       <c r="A181" s="65">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B181" s="66" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="C181" s="66" t="s">
         <v>286</v>
@@ -10857,13 +10906,13 @@
     </row>
     <row r="182" spans="1:8">
       <c r="A182" s="65">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B182" s="66" t="s">
-        <v>120</v>
+        <v>287</v>
       </c>
       <c r="C182" s="66" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D182" s="66" t="s">
         <v>26</v>
@@ -10879,13 +10928,13 @@
     </row>
     <row r="183" spans="1:8">
       <c r="A183" s="65">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B183" s="66" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C183" s="66" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D183" s="66" t="s">
         <v>26</v>
@@ -10901,13 +10950,13 @@
     </row>
     <row r="184" spans="1:8">
       <c r="A184" s="65">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B184" s="66" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C184" s="66" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D184" s="66" t="s">
         <v>26</v>
@@ -10923,10 +10972,10 @@
     </row>
     <row r="185" spans="1:8">
       <c r="A185" s="65">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B185" s="66" t="s">
-        <v>292</v>
+        <v>33</v>
       </c>
       <c r="C185" s="66" t="s">
         <v>293</v>
@@ -10945,10 +10994,10 @@
     </row>
     <row r="186" spans="1:8">
       <c r="A186" s="65">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B186" s="66" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C186" s="66" t="s">
         <v>294</v>
@@ -10967,13 +11016,13 @@
     </row>
     <row r="187" spans="1:8">
       <c r="A187" s="65">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B187" s="66" t="s">
-        <v>70</v>
+        <v>161</v>
       </c>
       <c r="C187" s="66" t="s">
-        <v>295</v>
+        <v>66</v>
       </c>
       <c r="D187" s="66" t="s">
         <v>26</v>
@@ -10989,13 +11038,13 @@
     </row>
     <row r="188" spans="1:8">
       <c r="A188" s="65">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B188" s="66" t="s">
-        <v>162</v>
+        <v>295</v>
       </c>
       <c r="C188" s="66" t="s">
-        <v>67</v>
+        <v>296</v>
       </c>
       <c r="D188" s="66" t="s">
         <v>26</v>
@@ -11011,10 +11060,10 @@
     </row>
     <row r="189" spans="1:8">
       <c r="A189" s="65">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B189" s="66" t="s">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="C189" s="66" t="s">
         <v>297</v>
@@ -11033,10 +11082,10 @@
     </row>
     <row r="190" spans="1:8">
       <c r="A190" s="65">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B190" s="66" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C190" s="66" t="s">
         <v>298</v>
@@ -11055,10 +11104,10 @@
     </row>
     <row r="191" spans="1:8">
       <c r="A191" s="65">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B191" s="66" t="s">
-        <v>267</v>
+        <v>32</v>
       </c>
       <c r="C191" s="66" t="s">
         <v>299</v>
@@ -11077,13 +11126,13 @@
     </row>
     <row r="192" spans="1:8">
       <c r="A192" s="65">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B192" s="66" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="C192" s="66" t="s">
-        <v>300</v>
+        <v>84</v>
       </c>
       <c r="D192" s="66" t="s">
         <v>26</v>
@@ -11094,18 +11143,18 @@
         <v>27</v>
       </c>
       <c r="H192" s="66">
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="193" spans="1:8">
       <c r="A193" s="65">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B193" s="66" t="s">
-        <v>134</v>
+        <v>300</v>
       </c>
       <c r="C193" s="66" t="s">
-        <v>85</v>
+        <v>301</v>
       </c>
       <c r="D193" s="66" t="s">
         <v>26</v>
@@ -11116,18 +11165,18 @@
         <v>27</v>
       </c>
       <c r="H193" s="66">
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="194" spans="1:8">
       <c r="A194" s="65">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B194" s="66" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C194" s="66" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D194" s="66" t="s">
         <v>26</v>
@@ -11143,10 +11192,10 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195" s="65">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B195" s="66" t="s">
-        <v>303</v>
+        <v>281</v>
       </c>
       <c r="C195" s="66" t="s">
         <v>304</v>
@@ -11165,13 +11214,13 @@
     </row>
     <row r="196" spans="1:8">
       <c r="A196" s="65">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B196" s="66" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="C196" s="66" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D196" s="66" t="s">
         <v>26</v>
@@ -11182,18 +11231,18 @@
         <v>27</v>
       </c>
       <c r="H196" s="66">
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="65">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B197" s="66" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C197" s="66" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D197" s="66" t="s">
         <v>26</v>
@@ -11204,15 +11253,15 @@
         <v>27</v>
       </c>
       <c r="H197" s="66">
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" s="65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B198" s="66" t="s">
-        <v>308</v>
+        <v>145</v>
       </c>
       <c r="C198" s="66" t="s">
         <v>309</v>
@@ -11231,13 +11280,13 @@
     </row>
     <row r="199" spans="1:8">
       <c r="A199" s="65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B199" s="66" t="s">
-        <v>146</v>
+        <v>310</v>
       </c>
       <c r="C199" s="66" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D199" s="66" t="s">
         <v>26</v>
@@ -11248,15 +11297,15 @@
         <v>27</v>
       </c>
       <c r="H199" s="66">
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B200" s="66" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="C200" s="66" t="s">
         <v>312</v>
@@ -11275,10 +11324,10 @@
     </row>
     <row r="201" spans="1:8">
       <c r="A201" s="65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B201" s="66" t="s">
-        <v>301</v>
+        <v>43</v>
       </c>
       <c r="C201" s="66" t="s">
         <v>313</v>
@@ -11292,28 +11341,6 @@
         <v>27</v>
       </c>
       <c r="H201" s="66">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8">
-      <c r="A202" s="65">
-        <v>1</v>
-      </c>
-      <c r="B202" s="66" t="s">
-        <v>43</v>
-      </c>
-      <c r="C202" s="66" t="s">
-        <v>314</v>
-      </c>
-      <c r="D202" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="E202" s="66"/>
-      <c r="F202" s="66"/>
-      <c r="G202" s="66" t="s">
-        <v>27</v>
-      </c>
-      <c r="H202" s="66">
         <v>2018</v>
       </c>
     </row>
@@ -11347,12 +11374,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="65c2bc0e-c5e8-40e4-bab9-15d2dec035ea" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5d9224dd-c5a1-4b4b-9ce3-e39b1585e770">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11593,20 +11622,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="65c2bc0e-c5e8-40e4-bab9-15d2dec035ea" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5d9224dd-c5a1-4b4b-9ce3-e39b1585e770">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF807E5F-0316-41A5-B02A-298F22A9D1C0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{044ABAA8-F30A-4E9B-845D-6B89EE5AE21C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="5d9224dd-c5a1-4b4b-9ce3-e39b1585e770"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="65c2bc0e-c5e8-40e4-bab9-15d2dec035ea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11631,18 +11667,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{044ABAA8-F30A-4E9B-845D-6B89EE5AE21C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF807E5F-0316-41A5-B02A-298F22A9D1C0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="5d9224dd-c5a1-4b4b-9ce3-e39b1585e770"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="65c2bc0e-c5e8-40e4-bab9-15d2dec035ea"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>